--- a/tasks/finalpool/yt-transcript-afrobeat-song-list-excel-email/groundtruth_workspace/Afrobeat_Tracklist.xlsx
+++ b/tasks/finalpool/yt-transcript-afrobeat-song-list-excel-email/groundtruth_workspace/Afrobeat_Tracklist.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracklist" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Artist_Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Tracklist" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Artist_Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,23 +459,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ye</t>
+          <t>Oxygen</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Burna Boy</t>
+          <t>Boy Spyce</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>180</v>
+        <v>43</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Opening track, smooth Afropop groove</t>
+          <t>Breezy afropop opener</t>
         </is>
       </c>
     </row>
@@ -485,23 +485,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Essence</t>
+          <t>Be My Part</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wizkid ft Tems</t>
+          <t>Omah Lay</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>180</v>
+        <v>55</v>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>45</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fan favorite, global crossover hit</t>
+          <t>Mellow loverman groove</t>
         </is>
       </c>
     </row>
@@ -511,23 +511,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Calm Down</t>
+          <t>Mr Money</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rema</t>
+          <t>Shallipopi</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>390</v>
+        <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>195</v>
+        <v>62</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>High-energy Afropop anthem</t>
+          <t>Street-hop money flex</t>
         </is>
       </c>
     </row>
@@ -537,23 +537,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Love Nwantiti</t>
+          <t>Until the Night Is Over</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CKay</t>
+          <t>Wizkid</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>585</v>
+        <v>162</v>
       </c>
       <c r="E5" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Afropop crossover sensation</t>
+          <t>Dreamy slow-burn anthem</t>
         </is>
       </c>
     </row>
@@ -563,23 +563,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FEEL</t>
+          <t>Best Friend</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Ayra Starr</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>765</v>
+        <v>346</v>
       </c>
       <c r="E6" t="n">
-        <v>200</v>
+        <v>146</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>High energy crowd pleaser</t>
+          <t>Bright singalong hook</t>
         </is>
       </c>
     </row>
@@ -589,23 +589,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Woman</t>
+          <t>I Know What You Like</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rema</t>
+          <t>Fireboy DML</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>965</v>
+        <v>492</v>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>63</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dance floor anthem with island vibes</t>
+          <t>Silky mid-tempo cut</t>
         </is>
       </c>
     </row>
@@ -615,23 +615,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Champion Sound</t>
+          <t>Lesson</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wizkid</t>
+          <t>CKay</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1150</v>
+        <v>555</v>
       </c>
       <c r="E8" t="n">
-        <v>190</v>
+        <v>37</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Classic Afrobeats banger</t>
+          <t>Minimal amapiano interlude</t>
         </is>
       </c>
     </row>
@@ -641,23 +641,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Terminator</t>
+          <t>Only You</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Asake</t>
+          <t>Rema</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1340</v>
+        <v>592</v>
       </c>
       <c r="E9" t="n">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Street vibes with infectious rhythm</t>
+          <t>Hypnotic log-drum groove</t>
         </is>
       </c>
     </row>
@@ -667,23 +667,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Unavailable</t>
+          <t>When We Touch</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Ruger</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1515</v>
+        <v>742</v>
       </c>
       <c r="E10" t="n">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chart-topping melodic Afropop</t>
+          <t>Dancehall-tinged, ends on go-fire chant</t>
         </is>
       </c>
     </row>
@@ -693,23 +693,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>You Know This</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ayra Starr</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1710</v>
+        <v>913</v>
       </c>
       <c r="E11" t="n">
-        <v>180</v>
+        <v>137</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Female Afrobeats highlight</t>
+          <t>Confident pop-afrobeats</t>
         </is>
       </c>
     </row>
@@ -719,23 +719,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Organise</t>
+          <t>Deliver</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fireboy DML</t>
+          <t>Kelvib</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1890</v>
+        <v>1050</v>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smooth Afropop gem</t>
+          <t>Kelvib name-drop at 1075s</t>
         </is>
       </c>
     </row>
@@ -745,23 +745,75 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Last Last</t>
+          <t>Ring on Your Finger</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>Wande Coal</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1185</v>
+      </c>
+      <c r="E13" t="n">
+        <v>51</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Romantic slow jam</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Yeah Yeah Yeah</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>Burna Boy</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2075</v>
-      </c>
-      <c r="E13" t="n">
-        <v>200</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Closing track, emotional Afrobeats</t>
+      <c r="D14" t="n">
+        <v>1236</v>
+      </c>
+      <c r="E14" t="n">
+        <v>57</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Chant-driven groove</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>I Want Enjoy</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Asake</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1293</v>
+      </c>
+      <c r="E15" t="n">
+        <v>92</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Closing hustle anthem</t>
         </is>
       </c>
     </row>
@@ -776,7 +828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,118 +851,183 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Burna Boy</t>
+          <t>Boy Spyce</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>380</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Wizkid</t>
+          <t>Omah Lay</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>400</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Rema</t>
+          <t>Shallipopi</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>380</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Wizkid</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>395</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CKay</t>
+          <t>Ayra Starr</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>180</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Asake</t>
+          <t>Fireboy DML</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>175</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ayra Starr</t>
+          <t>CKay</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>180</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Fireboy DML</t>
+          <t>Rema</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>185</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Wizkid ft Tems</t>
+          <t>Ruger</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Davido</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Kelvib</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Wande Coal</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Burna Boy</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Asake</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
